--- a/TestData/Deposit_TestData.xlsx
+++ b/TestData/Deposit_TestData.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26.35" customWidth="1" style="2" min="1" max="1"/>
@@ -536,7 +536,7 @@
     <row r="2" ht="13.8" customHeight="1" s="3">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>E-Wallet Deposit</t>
+          <t>HKD deposit by FPS</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -549,8 +549,10 @@
           <t>12345678</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>100</v>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -577,29 +579,25 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>65345678234</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>65345678234</v>
       </c>
     </row>
     <row r="3" ht="13.8" customHeight="1" s="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>E-Wallet Deposit</t>
+          <t>PHP deposit by QR-PH</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -612,8 +610,10 @@
           <t>12345678</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>100</v>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -627,7 +627,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>GCASH</t>
+          <t>QR-PH</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
@@ -640,23 +640,507 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>65345678234</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>65345678234</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>BDT deposit by USDT</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>BDT</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>USDT-TRC 20</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>65345678234</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>MXN deposit by SPEI</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>SPEI</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>65345678234</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>BRL deposit by PIX</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>E-Wallet</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>PIX</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>65345678234</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>VND deposit by MOMO</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>E-Wallet</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>MOMO</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>65345678234</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>IDR deposit by QRIS</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>E-Wallet</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>QRIS</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>65345678234</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>THB deposit by PromptPay</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>E-Wallet</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>PromptPay</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>65345678234</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>MYR deposit by FPX</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>MYR</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>E-Wallet</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>FPX</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>65345678234</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>USD deposit by USDT</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>USDT-TRC 20</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>65345678234</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Test123</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>65345678234</v>
       </c>
     </row>
     <row r="1048574" ht="12.8" customHeight="1" s="3"/>
